--- a/docs/results.xlsx
+++ b/docs/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\babar\Learning Path\Machine learning Engineering\RAG\Project 01\local-rag\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC645AB6-E0F1-4576-8F4E-75C827718D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9BDAE9-9E8D-45EA-91E0-C75AA0DC3DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Query_ID</t>
   </si>
@@ -55,13 +55,28 @@
   </si>
   <si>
     <t>V2_Groundedness</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>How many annual leave days do employees receive?</t>
+  </si>
+  <si>
+    <t>Employees receive 25 days of paid annual leave per calendar year.</t>
+  </si>
+  <si>
+    <t>To answer this question, we need to look at the provided context... 25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,10 +93,17 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="14"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -127,6 +149,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -407,22 +430,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
     <col min="2" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" customWidth="1"/>
     <col min="8" max="8" width="24.5703125" customWidth="1"/>
     <col min="9" max="9" width="24.7109375" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="29.28515625" customWidth="1"/>
     <col min="11" max="11" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -454,6 +477,452 @@
         <v>9</v>
       </c>
       <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.80610000000000004</v>
+      </c>
+      <c r="G2" s="3">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/results.xlsx
+++ b/docs/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\babar\Learning Path\Machine learning Engineering\RAG\Project 01\local-rag\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9BDAE9-9E8D-45EA-91E0-C75AA0DC3DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAF5843-6800-499C-9270-4217D1E6CEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,7 +434,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="3" width="23" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
     <col min="4" max="4" width="38.7109375" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>

--- a/docs/results.xlsx
+++ b/docs/results.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\babar\Learning Path\Machine learning Engineering\RAG\Project 01\local-rag\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAF5843-6800-499C-9270-4217D1E6CEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4651679-F3D0-4A91-832B-90249B3D2FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="245">
   <si>
     <t>Query_ID</t>
   </si>
@@ -57,26 +58,716 @@
     <t>V2_Groundedness</t>
   </si>
   <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>Direct</t>
-  </si>
-  <si>
-    <t>How many annual leave days do employees receive?</t>
-  </si>
-  <si>
-    <t>Employees receive 25 days of paid annual leave per calendar year.</t>
-  </si>
-  <si>
-    <t>To answer this question, we need to look at the provided context... 25</t>
+    <t>RAG Ablation Study — Evaluation Dataset (50 Queries) | TechNova Knowledge Base</t>
+  </si>
+  <si>
+    <t>Query ID</t>
+  </si>
+  <si>
+    <t>Original User Query</t>
+  </si>
+  <si>
+    <t>Expected Ideal Behavior</t>
+  </si>
+  <si>
+    <t>Target Module Tested</t>
+  </si>
+  <si>
+    <t>Source Document</t>
+  </si>
+  <si>
+    <t>Ground-Truth Answer (Summary)</t>
+  </si>
+  <si>
+    <t>Q001</t>
+  </si>
+  <si>
+    <t>Direct / Explicit</t>
+  </si>
+  <si>
+    <t>How many annual leave days are full-time employees entitled to per year?</t>
+  </si>
+  <si>
+    <t>Return exact number (25 days) with context about public holidays.</t>
+  </si>
+  <si>
+    <t>Basic Dense Retrieval</t>
+  </si>
+  <si>
+    <t>HR-01</t>
+  </si>
+  <si>
+    <t>Full-time employees are entitled to 25 working days of paid annual leave per calendar year, in addition to public holidays.</t>
+  </si>
+  <si>
+    <t>Q002</t>
+  </si>
+  <si>
+    <t>What is the minimum advance notice required for requesting leave of 3 or more days?</t>
+  </si>
+  <si>
+    <t>Return exact notice period: 10 working days.</t>
+  </si>
+  <si>
+    <t>A minimum of 10 working days advance notice is required for leave of 3 days or more.</t>
+  </si>
+  <si>
+    <t>Q003</t>
+  </si>
+  <si>
+    <t>How many carry-over leave days are allowed to the next year?</t>
+  </si>
+  <si>
+    <t>Return exact carry-over limit: 5 days, used by 31 March.</t>
+  </si>
+  <si>
+    <t>Employees may carry over a maximum of 5 unused annual leave days, which must be used by 31 March of the following year.</t>
+  </si>
+  <si>
+    <t>Q004</t>
+  </si>
+  <si>
+    <t>What are the core office days under the hybrid work model?</t>
+  </si>
+  <si>
+    <t>List core days: Monday, Tuesday, Thursday.</t>
+  </si>
+  <si>
+    <t>HR-02</t>
+  </si>
+  <si>
+    <t>Core office days are Monday, Tuesday, and Thursday. Remote days are Wednesday and Friday.</t>
+  </si>
+  <si>
+    <t>Q005</t>
+  </si>
+  <si>
+    <t>How many paid sick days per year are employees entitled to?</t>
+  </si>
+  <si>
+    <t>Return: 10 paid sick days per year.</t>
+  </si>
+  <si>
+    <t>HR-03</t>
+  </si>
+  <si>
+    <t>Employees are entitled to 10 paid sick days per calendar year under the Sick Leave Act 2022.</t>
+  </si>
+  <si>
+    <t>Q006</t>
+  </si>
+  <si>
+    <t>How many weeks of paid maternity leave does TechNova provide?</t>
+  </si>
+  <si>
+    <t>First 16 weeks at 100%, weeks 17-26 at 50%.</t>
+  </si>
+  <si>
+    <t>HR-04</t>
+  </si>
+  <si>
+    <t>The first 16 weeks are paid at 100% of basic salary; weeks 17-26 are paid at 50%.</t>
+  </si>
+  <si>
+    <t>Q007</t>
+  </si>
+  <si>
+    <t>What is the naming convention for feature branches in Git?</t>
+  </si>
+  <si>
+    <t>Return: feature/&lt;ticket-id&gt;-&lt;short-description&gt;.</t>
+  </si>
+  <si>
+    <t>ENG-01</t>
+  </si>
+  <si>
+    <t>Feature branches must follow the format: feature/&lt;ticket-id&gt;-&lt;short-description&gt;.</t>
+  </si>
+  <si>
+    <t>Q008</t>
+  </si>
+  <si>
+    <t>How many peer approvals are required before a PR can be merged?</t>
+  </si>
+  <si>
+    <t>Return: 2 approvals minimum.</t>
+  </si>
+  <si>
+    <t>A minimum of 2 peer approvals is required before a pull request can be merged.</t>
+  </si>
+  <si>
+    <t>Q009</t>
+  </si>
+  <si>
+    <t>What is the production deployment approval process in the CI/CD pipeline?</t>
+  </si>
+  <si>
+    <t>Describe manual approval gate from Release Engineering group.</t>
+  </si>
+  <si>
+    <t>ENG-02</t>
+  </si>
+  <si>
+    <t>Production deployments require manual approval from at least one member of the Release Engineering group after all automated gates pass.</t>
+  </si>
+  <si>
+    <t>Q010</t>
+  </si>
+  <si>
+    <t>What is the access token expiry time for the API?</t>
+  </si>
+  <si>
+    <t>Return: 15 minutes.</t>
+  </si>
+  <si>
+    <t>ENG-03</t>
+  </si>
+  <si>
+    <t>Access tokens expire after 15 minutes. Refresh tokens expire after 7 days.</t>
+  </si>
+  <si>
+    <t>Q011</t>
+  </si>
+  <si>
+    <t>What is the minimum password length required by the password policy?</t>
+  </si>
+  <si>
+    <t>Return: 14 characters.</t>
+  </si>
+  <si>
+    <t>SEC-01</t>
+  </si>
+  <si>
+    <t>The minimum required password length is 14 characters.</t>
+  </si>
+  <si>
+    <t>Q012</t>
+  </si>
+  <si>
+    <t>After how many failed login attempts is an account locked?</t>
+  </si>
+  <si>
+    <t>Return: 5 consecutive failed attempts.</t>
+  </si>
+  <si>
+    <t>Accounts are locked after 5 consecutive failed login attempts, with a 30-minute lockout duration.</t>
+  </si>
+  <si>
+    <t>Q013</t>
+  </si>
+  <si>
+    <t>How long are employee HR records retained after departure?</t>
+  </si>
+  <si>
+    <t>Return: 7 years post-departure.</t>
+  </si>
+  <si>
+    <t>SEC-02</t>
+  </si>
+  <si>
+    <t>Employee HR records are retained for 7 years post-departure.</t>
+  </si>
+  <si>
+    <t>Q014</t>
+  </si>
+  <si>
+    <t>Who is the CEO of TechNova Solutions?</t>
+  </si>
+  <si>
+    <t>Return name: Dr. Sarah O'Connor.</t>
+  </si>
+  <si>
+    <t>COMP-01</t>
+  </si>
+  <si>
+    <t>Dr. Sarah O'Connor is the CEO of TechNova Solutions Ltd., having co-founded the company in 2015.</t>
+  </si>
+  <si>
+    <t>Q015</t>
+  </si>
+  <si>
+    <t>In what year was TechNova founded?</t>
+  </si>
+  <si>
+    <t>Return: 2015.</t>
+  </si>
+  <si>
+    <t>TechNova Solutions Ltd. was founded in 2015 in Dublin, Ireland.</t>
+  </si>
+  <si>
+    <t>Q016</t>
+  </si>
+  <si>
+    <t>What MFA methods are approved for corporate accounts?</t>
+  </si>
+  <si>
+    <t>List: TOTP apps (Google Authenticator, Authy), YubiKey. Not SMS.</t>
+  </si>
+  <si>
+    <t>Approved MFA methods are TOTP apps (Google Authenticator or Authy) or hardware keys (YubiKey). SMS-based MFA is not permitted.</t>
+  </si>
+  <si>
+    <t>Q017</t>
+  </si>
+  <si>
+    <t>How long must a data breach be reported to the DPO?</t>
+  </si>
+  <si>
+    <t>Return: within 24 hours of discovery.</t>
+  </si>
+  <si>
+    <t>Any suspected or confirmed data breach must be reported to the Data Protection Officer within 24 hours of discovery.</t>
+  </si>
+  <si>
+    <t>Q018</t>
+  </si>
+  <si>
+    <t>What is the monthly internet allowance for remote workers?</t>
+  </si>
+  <si>
+    <t>Return: EUR 30 per month.</t>
+  </si>
+  <si>
+    <t>A monthly internet allowance of EUR 30 is provided to all remote/hybrid employees via payroll.</t>
+  </si>
+  <si>
+    <t>Q019</t>
+  </si>
+  <si>
+    <t>What is the minimum code test coverage gate in the CI/CD pipeline?</t>
+  </si>
+  <si>
+    <t>Return: 80% coverage.</t>
+  </si>
+  <si>
+    <t>The unit test stage enforces a minimum 80% code coverage gate.</t>
+  </si>
+  <si>
+    <t>Q020</t>
+  </si>
+  <si>
+    <t>What HTTP status code is returned when the API rate limit is exceeded?</t>
+  </si>
+  <si>
+    <t>Return: HTTP 429 Too Many Requests.</t>
+  </si>
+  <si>
+    <t>Exceeding the rate limit returns HTTP 429 Too Many Requests.</t>
+  </si>
+  <si>
+    <t>Q021</t>
+  </si>
+  <si>
+    <t>Vague / Ambiguous</t>
+  </si>
+  <si>
+    <t>leave rules</t>
+  </si>
+  <si>
+    <t>Rewrite to precise query, retrieve Annual Leave Policy, return key entitlement facts.</t>
+  </si>
+  <si>
+    <t>Query Rewriter</t>
+  </si>
+  <si>
+    <t>Full-time employees get 25 days annual leave. Carry-over limit is 5 days. Requests need 10 days notice for 3+ days off.</t>
+  </si>
+  <si>
+    <t>Q022</t>
+  </si>
+  <si>
+    <t>that sick thing</t>
+  </si>
+  <si>
+    <t>Rewrite to: sick leave entitlement. Return 10 paid days, notification procedure.</t>
+  </si>
+  <si>
+    <t>Employees are entitled to 10 paid sick days per year. Notify manager by 9 AM. GP cert needed for 3+ day absences.</t>
+  </si>
+  <si>
+    <t>Q023</t>
+  </si>
+  <si>
+    <t>remote stuff</t>
+  </si>
+  <si>
+    <t>Rewrite to: remote work policy. Return hybrid model (3-2), equipment, core hours.</t>
+  </si>
+  <si>
+    <t>Default hybrid model is 3 office days, 2 remote. Core hours 10-16 IST. Company provides laptop and monitor.</t>
+  </si>
+  <si>
+    <t>Q024</t>
+  </si>
+  <si>
+    <t>password thing</t>
+  </si>
+  <si>
+    <t>Rewrite to: password policy requirements. Return min length, MFA, rotation.</t>
+  </si>
+  <si>
+    <t>Passwords must be 14+ characters with upper, lower, digit, and special char. Rotate every 90 days. MFA mandatory.</t>
+  </si>
+  <si>
+    <t>Q025</t>
+  </si>
+  <si>
+    <t>how do I push code</t>
+  </si>
+  <si>
+    <t>Rewrite to: Git workflow and branch push process. Return PR requirements.</t>
+  </si>
+  <si>
+    <t>Create feature branch from develop, follow commit conventions, open PR with 2 approvals needed, all CI checks must pass.</t>
+  </si>
+  <si>
+    <t>Q026</t>
+  </si>
+  <si>
+    <t>baby leave</t>
+  </si>
+  <si>
+    <t>Rewrite to: maternity paternity parental leave entitlements.</t>
+  </si>
+  <si>
+    <t>Maternity: 26 weeks (16 at 100%, 10 at 50%). Paternity: 2 weeks at 100%. Parent's leave: 9 weeks each parent.</t>
+  </si>
+  <si>
+    <t>Q027</t>
+  </si>
+  <si>
+    <t>who's in charge</t>
+  </si>
+  <si>
+    <t>Rewrite to: company leadership team. Return CEO, CTO names and roles.</t>
+  </si>
+  <si>
+    <t>CEO is Dr. Sarah O'Connor. CTO is James Kavanagh. CPO is Aoife Murphy. VP Engineering is Ravi Sharma.</t>
+  </si>
+  <si>
+    <t>Q028</t>
+  </si>
+  <si>
+    <t>data stuff</t>
+  </si>
+  <si>
+    <t>Rewrite to: data retention periods policy. Return schedule.</t>
+  </si>
+  <si>
+    <t>Employee HR records: 7 years. Email: 3 years. Security logs: 12 months. Financial: 7 years. CCTV: 30 days.</t>
+  </si>
+  <si>
+    <t>Q029</t>
+  </si>
+  <si>
+    <t>api token expired</t>
+  </si>
+  <si>
+    <t>Rewrite to: how to refresh an expired API access token. Return refresh endpoint.</t>
+  </si>
+  <si>
+    <t>POST to /auth/refresh with grant_type: refresh_token, your refresh_token, and client_id. Access tokens expire in 15 minutes.</t>
+  </si>
+  <si>
+    <t>Q030</t>
+  </si>
+  <si>
+    <t>deploy went wrong</t>
+  </si>
+  <si>
+    <t>Rewrite to: CI/CD rollback procedure. Return rollback steps.</t>
+  </si>
+  <si>
+    <t>Run Rollback workflow in GitHub Actions, select last known-good image tag. Auto-rollback triggers if health checks fail within 5 min post-deploy.</t>
+  </si>
+  <si>
+    <t>Q031</t>
+  </si>
+  <si>
+    <t>Conversational</t>
+  </si>
+  <si>
+    <t>Who is the CEO of TechNova? [Turn 1]</t>
+  </si>
+  <si>
+    <t>Return name: Dr. Sarah O'Connor. Store in memory.</t>
+  </si>
+  <si>
+    <t>Conversation Memory</t>
+  </si>
+  <si>
+    <t>Dr. Sarah O'Connor is the CEO.</t>
+  </si>
+  <si>
+    <t>Q032</t>
+  </si>
+  <si>
+    <t>When was she hired? [Turn 2, follows Q031]</t>
+  </si>
+  <si>
+    <t>Resolve 'she' to Dr. Sarah O'Connor. Return: co-founded in 2015.</t>
+  </si>
+  <si>
+    <t>Dr. Sarah O'Connor co-founded TechNova in 2015, so she has been CEO since the company's inception.</t>
+  </si>
+  <si>
+    <t>Q033</t>
+  </si>
+  <si>
+    <t>How many sick days do we get? [Turn 1]</t>
+  </si>
+  <si>
+    <t>Employees are entitled to 10 paid sick days per calendar year.</t>
+  </si>
+  <si>
+    <t>Q034</t>
+  </si>
+  <si>
+    <t>And what happens after I use them all? [Turn 2, follows Q033]</t>
+  </si>
+  <si>
+    <t>Resolve 'them' to sick days. Return extended sick leave provisions.</t>
+  </si>
+  <si>
+    <t>After 10 days, HR may extend sick pay at 50% salary for up to 20 additional days, subject to a medical report and HR Director approval.</t>
+  </si>
+  <si>
+    <t>Q035</t>
+  </si>
+  <si>
+    <t>What is our password rotation policy? [Turn 1]</t>
+  </si>
+  <si>
+    <t>Return: every 90 days, prompt 14 days before expiry.</t>
+  </si>
+  <si>
+    <t>Corporate account passwords must be changed every 90 days. The system prompts users 14 days before expiry.</t>
+  </si>
+  <si>
+    <t>Q036</t>
+  </si>
+  <si>
+    <t>What about service accounts? [Turn 2, follows Q035]</t>
+  </si>
+  <si>
+    <t>Resolve context: service account password rotation. Return: 180-day cycle.</t>
+  </si>
+  <si>
+    <t>Service accounts and API keys follow a 180-day rotation cycle managed by the Platform team.</t>
+  </si>
+  <si>
+    <t>Q037</t>
+  </si>
+  <si>
+    <t>Tell me about our parental leave. [Turn 1]</t>
+  </si>
+  <si>
+    <t>Return high-level overview of maternity, paternity, parent's leave.</t>
+  </si>
+  <si>
+    <t>Maternity: 26 weeks. Paternity: 2 weeks. Parent's leave: 9 weeks each. All paid at 100% basic salary for the primary period.</t>
+  </si>
+  <si>
+    <t>Q038</t>
+  </si>
+  <si>
+    <t>How does that compare to maternity specifically? [Turn 2, follows Q037]</t>
+  </si>
+  <si>
+    <t>Resolve 'that' to parent's leave. Compare to maternity leave entitlements.</t>
+  </si>
+  <si>
+    <t>Maternity is 26 weeks total vs. 9 weeks parent's leave. Maternity offers longer duration with a pay taper (50% for weeks 17-26), while parent's leave is fully paid.</t>
+  </si>
+  <si>
+    <t>Q039</t>
+  </si>
+  <si>
+    <t>What are the branch naming rules? [Turn 1]</t>
+  </si>
+  <si>
+    <t>Return Git branch naming conventions.</t>
+  </si>
+  <si>
+    <t>Feature: feature/&lt;ticket-id&gt;-&lt;desc&gt;. Bugfix: bugfix/&lt;id&gt;-&lt;desc&gt;. Hotfix: hotfix/&lt;id&gt;-&lt;desc&gt;. Release: release/&lt;version&gt;. Direct pushes to main are blocked.</t>
+  </si>
+  <si>
+    <t>Q040</t>
+  </si>
+  <si>
+    <t>And how many approvals do I need for that? [Turn 2, follows Q039]</t>
+  </si>
+  <si>
+    <t>Resolve 'that' to PR merge process. Return: 2 approvals.</t>
+  </si>
+  <si>
+    <t>A minimum of 2 peer approvals are required before any PR can be merged into develop or main.</t>
+  </si>
+  <si>
+    <t>Q041</t>
+  </si>
+  <si>
+    <t>Out-of-Bounds</t>
+  </si>
+  <si>
+    <t>How do I bake a chocolate cake?</t>
+  </si>
+  <si>
+    <t>Abstain: query is unrelated to corporate knowledge base.</t>
+  </si>
+  <si>
+    <t>Guardrails / Abstention</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>System should respond: I don't have sufficient information in the knowledge base to answer this question.</t>
+  </si>
+  <si>
+    <t>Q042</t>
+  </si>
+  <si>
+    <t>What is the capital of France?</t>
+  </si>
+  <si>
+    <t>Abstain: geography question not in knowledge base.</t>
+  </si>
+  <si>
+    <t>System should abstain. General knowledge not grounded in documents.</t>
+  </si>
+  <si>
+    <t>Q043</t>
+  </si>
+  <si>
+    <t>Who won the FIFA World Cup in 2022?</t>
+  </si>
+  <si>
+    <t>Abstain: sports query not in knowledge base.</t>
+  </si>
+  <si>
+    <t>System should abstain with low confidence score.</t>
+  </si>
+  <si>
+    <t>Q044</t>
+  </si>
+  <si>
+    <t>Explain quantum entanglement to me.</t>
+  </si>
+  <si>
+    <t>Abstain: physics topic not present in documents.</t>
+  </si>
+  <si>
+    <t>System should respond with abstention message.</t>
+  </si>
+  <si>
+    <t>Q045</t>
+  </si>
+  <si>
+    <t>What is the best Python framework for web development?</t>
+  </si>
+  <si>
+    <t>Abstain: general tech opinion not in knowledge base.</t>
+  </si>
+  <si>
+    <t>System should abstain; no relevant chunks will be retrieved.</t>
+  </si>
+  <si>
+    <t>Q046</t>
+  </si>
+  <si>
+    <t>Can you recommend a good restaurant in Dublin?</t>
+  </si>
+  <si>
+    <t>Abstain: restaurant recommendation not in knowledge base.</t>
+  </si>
+  <si>
+    <t>Cosine similarity will be very low across all chunks. System must abstain.</t>
+  </si>
+  <si>
+    <t>Q047</t>
+  </si>
+  <si>
+    <t>Write me a poem about software engineers.</t>
+  </si>
+  <si>
+    <t>Abstain: creative writing request not grounded in documents.</t>
+  </si>
+  <si>
+    <t>System should abstain. No relevant chunks.</t>
+  </si>
+  <si>
+    <t>Q048</t>
+  </si>
+  <si>
+    <t>What is the stock price of Apple today?</t>
+  </si>
+  <si>
+    <t>Abstain: financial market data not in knowledge base.</t>
+  </si>
+  <si>
+    <t>System should abstain with low confidence score below threshold.</t>
+  </si>
+  <si>
+    <t>Q049</t>
+  </si>
+  <si>
+    <t>How many planets are in the solar system?</t>
+  </si>
+  <si>
+    <t>Abstain: astronomy query not in knowledge base.</t>
+  </si>
+  <si>
+    <t>System should return abstention response.</t>
+  </si>
+  <si>
+    <t>Q050</t>
+  </si>
+  <si>
+    <t>Tell me a joke.</t>
+  </si>
+  <si>
+    <t>Abstain: entertainment request not grounded in documents.</t>
+  </si>
+  <si>
+    <t>System should respond: I don't have information in my knowledge base to answer this.</t>
+  </si>
+  <si>
+    <t>Q01</t>
+  </si>
+  <si>
+    <t>There is no information provided in the context about account lockout after a certain number of failed login attempts.</t>
+  </si>
+  <si>
+    <t>Q02</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Dataset A: Fully specified queries</t>
+  </si>
+  <si>
+    <t>Example:</t>
+  </si>
+  <si>
+    <t>What are the hotfix deployment rules?</t>
+  </si>
+  <si>
+    <t>Expected result:</t>
+  </si>
+  <si>
+    <t>Query rewriting ≈ no improvement</t>
+  </si>
+  <si>
+    <t>Dataset B: Conversational follow-ups</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,16 +796,117 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1A3C6E"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF2E5FA3"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF856404"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1E6B3C"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF8B1A1A"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri "/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A3C6E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E5FA3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDDEDE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -137,11 +929,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -150,6 +957,49 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,7 +1281,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -446,7 +1296,7 @@
     <col min="11" max="11" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="18.75" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -479,34 +1329,36 @@
       </c>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>235</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.80610000000000004</v>
+        <v>236</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.29399999999999998</v>
       </c>
       <c r="G2" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
+    <row r="3" spans="1:11" ht="18.75">
+      <c r="A3" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -517,7 +1369,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="18.75">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -529,7 +1381,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="18.75">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -541,7 +1393,7 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="18.75">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -553,7 +1405,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18.75">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -565,7 +1417,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="18.75">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -577,7 +1429,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="18.75">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -589,8 +1441,10 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
+    <row r="10" spans="1:11" ht="18.75">
+      <c r="A10" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -601,8 +1455,10 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
+    <row r="11" spans="1:11" ht="18.75">
+      <c r="A11" s="17" t="s">
+        <v>239</v>
+      </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -613,8 +1469,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
+    <row r="12" spans="1:11" ht="18.75">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -625,8 +1480,10 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+    <row r="13" spans="1:11" ht="18.75">
+      <c r="A13" t="s">
+        <v>240</v>
+      </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -637,8 +1494,8 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+    <row r="14" spans="1:11" ht="18.75">
+      <c r="A14" s="18"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -649,8 +1506,10 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+    <row r="15" spans="1:11" ht="18.75">
+      <c r="A15" s="18" t="s">
+        <v>241</v>
+      </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -661,8 +1520,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
+    <row r="16" spans="1:11" ht="18.75">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -673,8 +1531,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
+    <row r="17" spans="1:10" ht="18.75">
+      <c r="A17" t="s">
+        <v>242</v>
+      </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -685,8 +1545,8 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
+    <row r="18" spans="1:10" ht="18.75">
+      <c r="A18" s="18"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -697,8 +1557,10 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
+    <row r="19" spans="1:10" ht="18.75">
+      <c r="A19" s="18" t="s">
+        <v>243</v>
+      </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -709,8 +1571,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
+    <row r="20" spans="1:10" ht="18.75">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -721,8 +1582,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
+    <row r="21" spans="1:10" ht="18.75">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -733,8 +1593,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
+    <row r="22" spans="1:10" ht="18.75">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -745,8 +1604,10 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
+    <row r="23" spans="1:10" ht="18.75">
+      <c r="A23" s="17" t="s">
+        <v>244</v>
+      </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -757,8 +1618,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
+    <row r="24" spans="1:10" ht="18.75">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -769,7 +1629,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="18.75">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -781,7 +1641,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="18.75">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -793,7 +1653,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="18.75">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -805,7 +1665,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="18.75">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -817,7 +1677,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="18.75">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -829,7 +1689,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="18.75">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -841,7 +1701,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="18.75">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -853,7 +1713,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="18.75">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -865,7 +1725,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="18.75">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -877,7 +1737,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="18.75">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -889,7 +1749,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="18.75">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -901,7 +1761,7 @@
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" ht="18.75">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -913,7 +1773,7 @@
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="18.75">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -927,5 +1787,1212 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53284663-78ED-4722-8538-5FBF1DE02BEA}">
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" customWidth="1"/>
+    <col min="4" max="4" width="30.140625" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" customWidth="1"/>
+    <col min="6" max="6" width="27.7109375" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="36">
+      <c r="A3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="48">
+      <c r="A4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="36">
+      <c r="A5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="24">
+      <c r="A6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="36">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="36">
+      <c r="A8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36">
+      <c r="A9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36">
+      <c r="A10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36">
+      <c r="A11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="24">
+      <c r="A12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36">
+      <c r="A13" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="36">
+      <c r="A14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="36">
+      <c r="A15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="24">
+      <c r="A16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="24">
+      <c r="A17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="36">
+      <c r="A18" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="24">
+      <c r="A19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="36">
+      <c r="A20" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="36">
+      <c r="A21" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="36">
+      <c r="A22" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="36">
+      <c r="A23" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="36">
+      <c r="A24" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="36">
+      <c r="A25" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="36">
+      <c r="A26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="36">
+      <c r="A27" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="24">
+      <c r="A28" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="36">
+      <c r="A29" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="24">
+      <c r="A30" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="36">
+      <c r="A31" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="36">
+      <c r="A32" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="24">
+      <c r="A33" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="24">
+      <c r="A34" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="24">
+      <c r="A35" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="36">
+      <c r="A36" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="24">
+      <c r="A37" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="36">
+      <c r="A38" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="24">
+      <c r="A39" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="36">
+      <c r="A40" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="36">
+      <c r="A41" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="36">
+      <c r="A42" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="24">
+      <c r="A43" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="24">
+      <c r="A44" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="24">
+      <c r="A45" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="24">
+      <c r="A46" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="36">
+      <c r="A47" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="36">
+      <c r="A48" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="24">
+      <c r="A49" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="24">
+      <c r="A50" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="24">
+      <c r="A51" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="24">
+      <c r="A52" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/results.xlsx
+++ b/docs/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\babar\Learning Path\Machine learning Engineering\RAG\Project 01\local-rag\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4651679-F3D0-4A91-832B-90249B3D2FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2526FA-ACA5-48D8-9FDF-D89F6DA3DFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="239">
   <si>
     <t>Query_ID</t>
   </si>
@@ -742,25 +742,7 @@
     <t>Q02</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Dataset A: Fully specified queries</t>
-  </si>
-  <si>
-    <t>Example:</t>
-  </si>
-  <si>
-    <t>What are the hotfix deployment rules?</t>
-  </si>
-  <si>
-    <t>Expected result:</t>
-  </si>
-  <si>
-    <t>Query rewriting ≈ no improvement</t>
-  </si>
-  <si>
-    <t>Dataset B: Conversational follow-ups</t>
+    <t>Query IDEveryday User QuestionStrategy CaseOutput of Query Rewriter (The Search String)Retrieved Chunk IDVector Similarity ScoreFinal Answer Quality (Pass/Fail)Q1[Insert Question 1]Case 1: BaselineIdentical to User QuestionNone / WrongLow (e.g., 0.45)❌ Fail (Info Missing)Case 2: Keywords[Paste generated keyword string]COMP-04High (e.g., 0.78)Pass (Accurate)Case 3: HyDE[Paste generated fake answer para]COMP-04Highest (e.g., 0.88)🏆 Pass (Authoritative)Q2[Insert Question 2]Case 1: BaselineIdentical to User QuestionNone / WrongLow❌ Fail (Info Missing)Case 2: Keywords[Paste generated keyword string]COMP-04HighPass (Accurate)Case 3: HyDE[Paste generated fake answer para]COMP-04Highest🏆 Pass (Authoritative)</t>
   </si>
 </sst>
 </file>
@@ -1456,9 +1438,7 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:11" ht="18.75">
-      <c r="A11" s="17" t="s">
-        <v>239</v>
-      </c>
+      <c r="A11" s="17"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -1481,9 +1461,6 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:11" ht="18.75">
-      <c r="A13" t="s">
-        <v>240</v>
-      </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -1507,9 +1484,7 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:11" ht="18.75">
-      <c r="A15" s="18" t="s">
-        <v>241</v>
-      </c>
+      <c r="A15" s="18"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -1532,9 +1507,6 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10" ht="18.75">
-      <c r="A17" t="s">
-        <v>242</v>
-      </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -1558,9 +1530,7 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="18.75">
-      <c r="A19" s="18" t="s">
-        <v>243</v>
-      </c>
+      <c r="A19" s="18"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1605,9 +1575,7 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" ht="18.75">
-      <c r="A23" s="17" t="s">
-        <v>244</v>
-      </c>
+      <c r="A23" s="17"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>

--- a/docs/results.xlsx
+++ b/docs/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\babar\Learning Path\Machine learning Engineering\RAG\Project 01\local-rag\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2526FA-ACA5-48D8-9FDF-D89F6DA3DFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC479DF9-A126-4320-9E22-620330C4DCDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,38 +26,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="239">
-  <si>
-    <t>Query_ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="334">
   <si>
     <t>Category</t>
   </si>
   <si>
-    <t>User_Query</t>
-  </si>
-  <si>
-    <t>Ground_Truth_Answer</t>
-  </si>
-  <si>
-    <t>V1_Answer</t>
-  </si>
-  <si>
-    <t>V1_Confidence</t>
-  </si>
-  <si>
-    <t>V1_Groundedness</t>
-  </si>
-  <si>
-    <t>V2_Answer</t>
-  </si>
-  <si>
-    <t>V2_Confidence</t>
-  </si>
-  <si>
-    <t>V2_Groundedness</t>
-  </si>
-  <si>
     <t>RAG Ablation Study — Evaluation Dataset (50 Queries) | TechNova Knowledge Base</t>
   </si>
   <si>
@@ -733,23 +706,506 @@
     <t>System should respond: I don't have information in my knowledge base to answer this.</t>
   </si>
   <si>
-    <t>Q01</t>
-  </si>
-  <si>
-    <t>There is no information provided in the context about account lockout after a certain number of failed login attempts.</t>
-  </si>
-  <si>
-    <t>Q02</t>
-  </si>
-  <si>
-    <t>Query IDEveryday User QuestionStrategy CaseOutput of Query Rewriter (The Search String)Retrieved Chunk IDVector Similarity ScoreFinal Answer Quality (Pass/Fail)Q1[Insert Question 1]Case 1: BaselineIdentical to User QuestionNone / WrongLow (e.g., 0.45)❌ Fail (Info Missing)Case 2: Keywords[Paste generated keyword string]COMP-04High (e.g., 0.78)Pass (Accurate)Case 3: HyDE[Paste generated fake answer para]COMP-04Highest (e.g., 0.88)🏆 Pass (Authoritative)Q2[Insert Question 2]Case 1: BaselineIdentical to User QuestionNone / WrongLow❌ Fail (Info Missing)Case 2: Keywords[Paste generated keyword string]COMP-04HighPass (Accurate)Case 3: HyDE[Paste generated fake answer para]COMP-04Highest🏆 Pass (Authoritative)</t>
+    <t>Everyday User Question</t>
+  </si>
+  <si>
+    <t>Strategy Case</t>
+  </si>
+  <si>
+    <t>Output of Query Rewriter (The Search String)</t>
+  </si>
+  <si>
+    <t>Retrieved Chunk ID</t>
+  </si>
+  <si>
+    <t>Vector Similarity Score</t>
+  </si>
+  <si>
+    <t>Final Answer Quality (Pass/Fail)</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Case 1: Baseline</t>
+  </si>
+  <si>
+    <t>❌ Fail (Info Missing)</t>
+  </si>
+  <si>
+    <t>Case 2: Keywords</t>
+  </si>
+  <si>
+    <t>Pass (Accurate)</t>
+  </si>
+  <si>
+    <t>Case 3: HyDE</t>
+  </si>
+  <si>
+    <t>🏆 Pass (Authoritative)</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Turn 1: Let's review the validation and pipeline injection safeguards on Page 3. \n Turn 2: What exactly takes place if it fails to clear every single one of them?</t>
+  </si>
+  <si>
+    <t>What exactly takes place if it fails to clear every single one of them? (Since it doesn't rewrite, it just passes the raw Turn 2 or appends blindly).</t>
+  </si>
+  <si>
+    <t>[GOV-LIFE-4.2] (Page 5)</t>
+  </si>
+  <si>
+    <t>❌ Fail (Irrelevant Context / Retrieval Error)</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>There is no information in the provided context to answer the question. The conversation history mentions a question about validation and pipeline injection safeguards on Page 3, but the context provided does not include Page 3. It appears to be from a different part of the document (p.5) and discusses data erasure and compliance auditing. Therefore, I cannot provide a specific answer to the question based on the given context.</t>
+  </si>
+  <si>
+    <t>deployment failure patch rejection automated testing failure integrity gate failure regression testing failure production deployment block hotfix failure validation sequence failure live execution prevention core system behavior evaluation failure</t>
+  </si>
+  <si>
+    <t>[ENG-CTRL-3.1] (Page 3)</t>
+  </si>
+  <si>
+    <t>High (0.73)</t>
+  </si>
+  <si>
+    <t>Low (0.40)</t>
+  </si>
+  <si>
+    <t>If the hotfix fails to pass 100% of the automated integrity gates, the production deployment is not allowed to proceed.</t>
+  </si>
+  <si>
+    <t>Turn 1: Show me Section 2 on Page 1 regarding the operational coverage standards and accrual mechanics. \n Turn 2: What automated action occurs if someone asks for more than what is registered there?</t>
+  </si>
+  <si>
+    <t>What automated action occurs if someone asks for more than what is registered there?</t>
+  </si>
+  <si>
+    <t>Low (0.31)</t>
+  </si>
+  <si>
+    <t>The context does not explicitly state what automated action occurs if someone asks for more than what is registered. The provided text discusses the operational coverage standards, accrual mechanics, and other topics, but it does not directly address the question. Therefore, the answer cannot be determined based on the given context.</t>
+  </si>
+  <si>
+    <t>automated action request denial exceeding limits registered capacity scheduling matrix automated system capacity evaluation real-time capacity project milestones temporary exit production ecosystem accrual tracking fractional credits</t>
+  </si>
+  <si>
+    <t>[HR-GOV-1.1] (Page 1)</t>
+  </si>
+  <si>
+    <t>Medium (0.59)</t>
+  </si>
+  <si>
+    <t>The internal compliance engine will automatically trigger an administrative hold, requiring a secondary review by the regional human resources director.</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Turn 1: Look at Subsection A on Page 2 regarding Immediate Incident Logging. \n Turn 2: What is the exact chronological cutoff mandated for this?</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> What is the exact chronological cutoff mandated for this?</t>
+  </si>
+  <si>
+    <t>[GOV-LIFE-4.2] (Page 4) / Faulty Retrieval</t>
+  </si>
+  <si>
+    <t>Low (0.39)</t>
+  </si>
+  <si>
+    <t>Pass via History (Retrieval Failure)</t>
+  </si>
+  <si>
+    <t>Retriever failed to find the target data point. The generator successfully answered exclusively by extracting "07:30 AM" from the Turn 1 conversational history buffer. "Our evaluation reveals a critical distinction between retrieval success and generation accuracy in multi-turn RAG. In Sequence 3, the baseline retriever failed completely to return relevant documents. However, because the information was implicitly seeded into the chat history during Turn 1, the generation model bypassed the retrieval failure. Advanced query rewriting eliminates this structural dependency by ensuring true real-time retrieval convergence (increasing top-1 similarity from 0.39 to 0.63)."</t>
+  </si>
+  <si>
+    <t>The exact chronological cutoff mandated is before the 07:30 AM morning call-in deadline.</t>
+  </si>
+  <si>
+    <t>chronological cutoff deadline time limit reporting deadline morning deadline cutoff time mandated deadline time constraint incident reporting absence reporting AMI reporting physiological disruption psychological disruption health disruption workforce management shift commanders resource deficit</t>
+  </si>
+  <si>
+    <t>[MED-FRAME-2.4] (Page 2) / Valid Retrieval</t>
+  </si>
+  <si>
+    <t>Medium (0.63)</t>
+  </si>
+  <si>
+    <t>Pass (True Retrieval Success)</t>
+  </si>
+  <si>
+    <t>07:30 AM</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Turn 1: Let's check the mitigation of dependency bottlenecks on Page 1. \n Turn 2: Who assumes full responsibility during that specific administrative duration?</t>
+  </si>
+  <si>
+    <t>Who assumes full responsibility during that specific administrative duration?</t>
+  </si>
+  <si>
+    <t>[HR-GOV-1.1] (Page 2) / Valid Retrieval</t>
+  </si>
+  <si>
+    <t>low (0.46)</t>
+  </si>
+  <si>
+    <t>Pass (Accurate Grounding)</t>
+  </si>
+  <si>
+    <t>The secondary resource, designated as a proxy, assumes full administrative accountability for the duration of the principal's Voluntary Terminal Downtime.</t>
+  </si>
+  <si>
+    <t>responsibility assumption administrative duration full responsibility accountability leadership oversight management authority decision-making power role designation period timeframe specific interval assigned duties legal liability contractual obligations governance structure executive authority senior management operational control strategic direction compliance adherence fiduciary duty ultimate accountability</t>
+  </si>
+  <si>
+    <t>[MED-FRAME-2.4] (Page 3) / Faulty Retrieval</t>
+  </si>
+  <si>
+    <t>low (0.48)</t>
+  </si>
+  <si>
+    <t>❌ Fail (Context Pollution / Hallucination)</t>
+  </si>
+  <si>
+    <t>The corporate benefits and risk mitigation team assumes full responsibility during that specific administrative duration, which occurs when the duration of the documented AMI extends beyond seven consecutive calendar days.</t>
+  </si>
+  <si>
+    <t>"Our empirical testing exposed a vital vulnerability in pre-retrieval query rewriting (Case 2), which we define as 'Semantic Over-Expansion.' In Sequence 4, while the baseline's dense retriever cleanly mapped semantic tokens to the target text, the Query Rewriter over-parameterized the history, injecting cross-domain tokens from alternate policy grids (AMI instead of VTD). This polluted the retrieval phase, driving a top-1 context mismatch and inducing an downstream generation hallucination."</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>Turn 1: Review Section 3.1.1 on Page 3 regarding critical infrastructure remediation mechanics. \n Turn 2: Under what specific escalation criteria is this shortcut authorized?</t>
+  </si>
+  <si>
+    <t>Under what specific escalation criteria is this shortcut authorized?</t>
+  </si>
+  <si>
+    <t>low (0.43)</t>
+  </si>
+  <si>
+    <t>❌ Fail (Retrieval Error / Passed via History)</t>
+  </si>
+  <si>
+    <t>Retriever completely missed Page 3 due to pronoun ambiguity. Downstream generator compensated via chat buffer.</t>
+  </si>
+  <si>
+    <t>"Our final evaluation sequence (Sequence 5) revealed a critical boundary limitation of pre-retrieval query rewriting, which we define as 'Semantic Dilution in Dense Vector Indexing.' While the LLM successfully expanded the ambiguous question into a highly comprehensive keyword string, the dense embedding engine failed to register a higher cosine similarity for the target page. The influx of descriptive, yet high-frequency enterprise tokens (e.g., 'continuity', 'mechanism') caused a vector alignment drift toward over-clustered nodes on Pages 1 and 2. This proves that query expansion can inadvertently increase retrieval noise in homogeneous technical datasets, making a strong academic argument for post-retrieval re-ranking mechanisms."</t>
+  </si>
+  <si>
+    <t>escalation criteria shortcut authorization P1 incident incident escalation catastrophic system degradation severe security anomaly emergency mechanism bypass standard release cycles data integrity business continuity service disruption</t>
+  </si>
+  <si>
+    <t>(Page 1) / Retrieval Deficit</t>
+  </si>
+  <si>
+    <t>❌ Fail (Retrieval Deficit / Passed via History)</t>
+  </si>
+  <si>
+    <t>The Query Rewriter successfully expanded the query, but the dense retriever failed to isolate Page 3 due to semantic dilution. Highly descriptive tokens were overwhelmed by shared enterprise jargon across Pages 1 and 2.</t>
+  </si>
+  <si>
+    <t>Should any automated integrity gate within the abbreviated validation sequence fail, the deployment is immediately quarantined. The Rapid Patchwork Protocol mandates that a failed validation triggers an automated rollback to the last known stable production build and generates a critical alert to the incident response team for immediate analysis and remediation. Further deployment attempts of the failed patch are blocked until the underlying failure is identified and rectified.</t>
+  </si>
+  <si>
+    <t>(ENG-CTRL-3.1) (Page 3, Source 1)</t>
+  </si>
+  <si>
+    <t>High (0.74)</t>
+  </si>
+  <si>
+    <t>HyDE resolves the pronoun deficit by synthesizing an aligned technical hypothesis. However, the rewriter exhibits extreme semantic drift by hallucinating non-existent protocols (quarantines, rollbacks). The pass is secured solely by strict downstream generation constraints that filtered out the rewriter's hallucinations (context).</t>
+  </si>
+  <si>
+    <t>The automated scheduling matrix will flag any VTD requests exceeding the fifteen percent departmental threshold or conflicting with critical project milestones, automatically denying the request and initiating a notification to the requesting employee's direct supervisor. Subsequent manual review by the department lead is required to assess the feasibility of alternative scheduling or resource allocation before any potential override can be considered</t>
+  </si>
+  <si>
+    <t>Medium (0.65)</t>
+  </si>
+  <si>
+    <t>❌ Fail (Over-Speculation / Wrong Context Retrieval / Info Missing)</t>
+  </si>
+  <si>
+    <t>The context does not explicitly state the automated action that occurs if someone asks for more than what is registered. It only mentions that the enterprise utilizes an automated, high-fidelity scheduling matrix that evaluates real-time capacity against projected project milestones before approving any temporary exit from the production ecosystem, and that no more than fifteen percent of a single department's localized workforce may be authorized for concurrent VTD at any given juncture. However, it does not specify what happens if someone exceeds this limit.</t>
+  </si>
+  <si>
+    <t>False Negative Retrieval / Windowing Deficit. The retriever successfully targeted Section 2, but a critical chunking boundary error clipped the paragraph early (p. 1). The downstream generator missed the target data point ("administrative hold") because it was sliced into a adjacent chunk not captured by the top-1 retrieval window (p. 1). HyDE suffered from an over-speculation trap. The generated hypothetical text anticipated an explicit system denial, creating an artificial vector alignment drift toward Page 1's percentage constraints while completely missing Page 2's administrative hold protocol.   Our testing reveals a structural vulnerability in Hypothetical Document Embeddings (Case 3), which we define as the 'Over-Speculation Divergence.' When the generated hypothetical answer describes a plausible but incorrect downstream operational procedure (e.g., predicting an immediate system denial instead of an administrative hold), the resultant embedding vector diverges from the true target block. This creates high-similarity mapping to adjacent, noisy policy constraints (Page 1) while completely blinding the pipeline to the factually grounded data substrate.</t>
+  </si>
+  <si>
+    <t>The centralized workforce management application mandates incident logging for Acute Medical Incapacitations (AMIs) to be completed prior to the 07:30 AM morning call-in deadline. Failure to adhere to this chronological cutoff will result in the incident not being officially recorded for immediate resource allocation purposes.</t>
+  </si>
+  <si>
+    <t>[MED-FRAME-2.4] (Page 2) / Target Lock</t>
+  </si>
+  <si>
+    <t>High (0.78)</t>
+  </si>
+  <si>
+    <t>07:30 AM morning call-in deadline.</t>
+  </si>
+  <si>
+    <t>HyDE demonstrates optimal alignment by precisely predicting the literal time string ("07:30 AM") and target acronym ("AMI") in the generated expansion. This eliminates the vocabulary gap entirely and forces a high vector proximity score to the target chunk on Page 2.
+HyDE achieved optimal vector convergence. By translating an abstract query into a domain-aligned answer template, the latent space similarity score expanded from 0.39 to 0.78, validating the efficacy of answer-to-document dense mapping.
+Our evaluation under Sequence 3 establishes the empirical superiority of Hypothetical Document Embeddings (Case 3) over traditional lexical approaches when handling dense conceptual boundaries. While the baseline dense vector space collapsed under abstract query parsing (Score: 0.3918), the zero-shot generation of a predictive answer structure effectively synchronized the query topography with the target compliance dataset. This alignment yielded a top-ranked, mathematically dominant retrieval match (Score: 0.7843) and eliminated the system's reliance on generation-phase context compensation.</t>
+  </si>
+  <si>
+    <t>During the specified administrative duration, the Chief Information Officer (CIO) assumes full responsibility for all operational and strategic decisions pertaining to the information technology infrastructure. This includes oversight of system integrity, data security, and the successful execution of all IT-related projects and initiatives. The CIO's authority is absolute for the defined period, ensuring unified command and control over critical technological resources.</t>
+  </si>
+  <si>
+    <t>[GOV-LIFE-4.2] (Page 4) / Retrieval Failure (It pulled high-level IT governance instead of VTD)</t>
+  </si>
+  <si>
+    <t>The secondary resource, a designated proxy, assumes full administrative accountability for the duration of the principal's Voluntary Terminal Downtime.</t>
+  </si>
+  <si>
+    <t>Generation-Phase Context Compensation. The retriever completely failed (scores &lt; 0.43) due to extreme HyDE semantic drift introducing a hallucinated 'CIO' persona. The final correct answer is an artifact of history buffer leakage; the generator extracted the answer from Turn 1's conversational state rather than the retrieved text chunks (context).</t>
+  </si>
+  <si>
+    <t>HyDE experienced an extreme entity misclassification trap. The hypothetical answer erroneously speculated that the Chief Information Officer (CIO) held the target administrative role, forcing a vector drift toward Page 4 IT governance metrics. Downstream generation accuracy was preserved strictly via generation-phase history leakage.</t>
+  </si>
+  <si>
+    <t>Our empirical findings across Sequences 2 and 4 define a clear operational boundary for Hypothetical Document Embeddings (HyDE). When a multi-turn user query is highly abstract and lacks distinct domain nouns, the zero-shot hypothetical answer engine relies on general semantic heuristics to guess the missing entity. If this guess introduces a completely misaligned operational role or procedure (e.g., speculating the 'Chief Information Officer' in Q4 or an 'immediate system denial' in Q2), the dense retriever experiences a catastrophic domain drift. This demonstrates that while HyDE excels at mapping abstract syntax to concrete technical times (as proven in Sequence 3's success), it introduces an uncontrollable point of failure when navigating ambiguous administrative hierarchies within homogeneous corporate document indices.</t>
+  </si>
+  <si>
+    <t>Low (0.42)</t>
+  </si>
+  <si>
+    <t>The Rapid Patchwork Protocol (RPP) is authorized solely under a P1 incident escalation, defined by active service disruption that demonstrably threatens data integrity or core business continuity. This designation requires explicit confirmation from the Incident Commander and the Chief Technology Officer, validating the immediate and severe impact on operational stability. Any deviation from these criteria necessitates a formal review and approval process, overriding the emergency authorization.</t>
+  </si>
+  <si>
+    <t>[ENG-CTRL-3.1] (Page 3) / Optimal Target Lock, Source 1 &amp; Source 2</t>
+  </si>
+  <si>
+    <t>High (0.82)</t>
+  </si>
+  <si>
+    <t>This shortcut, the Rapid Patchwork Protocol (RPP), is authorized under a P1 incident escalation, where active service disruption threatens data integrity or core business continuity.</t>
+  </si>
+  <si>
+    <t>HyDE demonstrates robust performance by bridging the vocabulary gap between the user's casual token ('shortcut') and the document's formal governance terminology ('Rapid Patchwork Protocol'). The expansion generates an exceptionally strong vector intersection with Page 3 infrastructure mechanics, eliminating any dependency on history leakage.</t>
+  </si>
+  <si>
+    <t>HyDE successfully eliminated the semantic dilution and pronoun ambiguity traps seen in the other strategies. By synthesizing a precise domain-aligned answer template, it achieved optimal vector alignment, increasing the similarity score from 0.43 (Baseline) to 0.82.</t>
+  </si>
+  <si>
+    <t>Strategic Summary Cheat Sheet (When to Use What)</t>
+  </si>
+  <si>
+    <r>
+      <t>Case 1 (Baseline) — Best For:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> High-efficiency, low-latency, isolated single-turn literal queries. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Worst For:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Complex multi-turn conversations where pronouns rely on past statements.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Case 2 (Keywords) — Best For:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Broad keyword matching when queries lack specific structure. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Worst For:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Dense, multi-topic compliance manuals where keywords overlap across different sections, leading to extreme cross-page pollution.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Case 3 (HyDE) — Best For:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Overcoming conversational shortcuts, hidden constraints, and pronouns by building a meaningful technical hypothesis. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Worst For:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Exacting environments sensitive to fabricated facts, or when documents have rigid paragraph chunk cutoffs.</t>
+    </r>
+  </si>
+  <si>
+    <t>4.3 Comparative Evaluation and Strategy Trade-offs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Our empirical analysis across five adversarial multi-turn evaluation sequences reveals distinct operational characteristics and vulnerabilities for each retrieval strategy architecture. The Baseline method (Case 1) consistently suffers from severe vocabulary mismatch and pronoun ambiguity during follow-up turns, yielding low vector similarity scores (ranging from 0.31 to 0.49). Despite these retrieval failures, the Baseline pipeline exhibits an artificial performance inflation due to </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Generation-Phase History Leakage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. When the chat history buffer carries information across turns, the downstream generator compensates for retrieval failures by extracting answers directly from prior turn states rather than the fetched context.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The Pre-retrieval Keyword Expansion engine (Case 2) demonstrates a catastrophic vulnerability to </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Context Pollution</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Semantic Drift</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. When presented with vague coreferences, the keyword generator frequently over-expands queries using irrelevant corporate jargon or terms lifted from entirely separate domains within the document set. This introduces cross-page contamination (e.g., matching human resources queries with critical infrastructure remediation protocols), causing the pipeline to fetch misleading chunks and generate false, ungrounded answers.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hypothetical Document Embeddings (HyDE, Case 3) consistently out-performs the other strategies in bridging the vocabulary gap by translating casual user phrases into formal technical nomenclature (e.g., resolving "shortcut" into "Rapid Patchwork Protocol"). HyDE achieves the highest true retrieval success rates with confident proximity scores exceeding 0.75. However, HyDE remains vulnerable to </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Algorithmic Over-Imagination</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, hallucinating fine-grained organizational hierarchies and workflows absent from the source documentation. Furthermore, its efficacy is bound by chunking granularity; if a target data point spans a truncated boundary, HyDE can fail despite high semantic alignment.</t>
+    </r>
+  </si>
+  <si>
+    <t>Irrelevant Match (Page 2)</t>
+  </si>
+  <si>
+    <t>Our empirical testing exposed three critical failure modes within multi-turn conversational RAG architectures. First, we identify \textit{Generation-Phase History Leakage} (observed in Q3 and Q5 under the Baseline case), where the generator LLM accurately answers a query despite a completely failed document retrieval phase. This occurs because target data points are implicitly seeded into the chat history during earlier turns, allowing the model to bypass database deficits. Second, we observe the \textit{Semantic Over-Expansion Trap} (observed in Q4 Keywords), where the query rewriter over-parameterizes historical context, injecting cross-domain tokens that pollute the retrieval phase and cause a downstream hallucination. Third, our results highlight the \textit{HyDE Over-Speculation Trap} (observed in Q2), proving that when a hypothetical answer template speculates an incorrect operational procedure or corporate entity, it induces a severe vector drift that blinds the retriever to the true grounding text.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -837,6 +1293,46 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri "/>
+    </font>
+    <font>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -930,7 +1426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -970,18 +1466,35 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1266,7 +1779,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="3" max="3" width="28.5703125" customWidth="1"/>
     <col min="4" max="4" width="38.7109375" customWidth="1"/>
     <col min="5" max="5" width="23.28515625" customWidth="1"/>
@@ -1278,233 +1791,436 @@
     <col min="11" max="11" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" thickBot="1">
+    <row r="1" spans="1:11" ht="36.75" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>226</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>227</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>228</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>229</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>6</v>
+        <v>231</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>244</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>74</v>
+        <v>240</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.29399999999999998</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3"/>
+        <v>242</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>245</v>
+      </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:11" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>237</v>
-      </c>
+      <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:11" ht="18.75">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:11" ht="18.75">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:11" ht="18.75">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>258</v>
+      </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:11" ht="18.75">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>305</v>
+      </c>
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:11" ht="18.75">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="A8" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:11" ht="18.75">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:11" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>238</v>
-      </c>
+      <c r="A10" s="3"/>
       <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="C10" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>310</v>
+      </c>
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:11" ht="18.75">
-      <c r="A11" s="17"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="A11" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:11" ht="18.75">
       <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:11" ht="18.75">
       <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="K13" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="18.75">
-      <c r="A14" s="18"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="A14" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>291</v>
+      </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:11" ht="18.75">
-      <c r="A15" s="18"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="C15" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>292</v>
+      </c>
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:11" ht="18.75">
       <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="C16" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="18.75">
       <c r="B17" s="3"/>
@@ -1518,7 +2234,7 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10" ht="18.75">
-      <c r="A18" s="18"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1530,7 +2246,7 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="18.75">
-      <c r="A19" s="18"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1541,54 +2257,57 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:10" ht="18.75">
-      <c r="B20" s="3"/>
+    <row r="20" spans="1:10" ht="19.5">
+      <c r="B20" s="22" t="s">
+        <v>324</v>
+      </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" ht="18.75">
-      <c r="B21" s="3"/>
+      <c r="B21" s="20" t="s">
+        <v>325</v>
+      </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" ht="18.75">
-      <c r="B22" s="3"/>
+      <c r="B22" s="20" t="s">
+        <v>326</v>
+      </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" ht="18.75">
-      <c r="A23" s="17"/>
-      <c r="B23" s="3"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="20" t="s">
+        <v>327</v>
+      </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" ht="18.75">
       <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1599,7 +2318,9 @@
     </row>
     <row r="25" spans="1:10" ht="18.75">
       <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="B25" s="21" t="s">
+        <v>328</v>
+      </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1611,7 +2332,9 @@
     </row>
     <row r="26" spans="1:10" ht="18.75">
       <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="B26" s="23" t="s">
+        <v>329</v>
+      </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1623,7 +2346,9 @@
     </row>
     <row r="27" spans="1:10" ht="18.75">
       <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+      <c r="B27" s="23" t="s">
+        <v>330</v>
+      </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1635,7 +2360,9 @@
     </row>
     <row r="28" spans="1:10" ht="18.75">
       <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+      <c r="B28" s="23" t="s">
+        <v>331</v>
+      </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1659,7 +2386,9 @@
     </row>
     <row r="30" spans="1:10" ht="18.75">
       <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+      <c r="B30" t="s">
+        <v>333</v>
+      </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1774,1187 +2503,1187 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="A1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="36">
       <c r="A3" s="5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="48">
       <c r="A4" s="5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="36">
       <c r="A5" s="5" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="24">
       <c r="A6" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="36">
       <c r="A7" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="36">
       <c r="A8" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="36">
       <c r="A9" s="5" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="36">
       <c r="A10" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="36">
       <c r="A11" s="5" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24">
       <c r="A12" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="36">
       <c r="A13" s="5" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="36">
       <c r="A14" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="36">
       <c r="A15" s="5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24">
       <c r="A16" s="5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24">
       <c r="A17" s="5" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="36">
       <c r="A18" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24">
       <c r="A19" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="36">
       <c r="A20" s="5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="36">
       <c r="A21" s="5" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="36">
       <c r="A22" s="5" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="36">
       <c r="A23" s="5" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="36">
       <c r="A24" s="5" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="36">
       <c r="A25" s="5" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="E25" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="36">
       <c r="A26" s="5" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="36">
       <c r="A27" s="5" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="24">
       <c r="A28" s="5" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="36">
       <c r="A29" s="5" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="24">
       <c r="A30" s="5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="36">
       <c r="A31" s="5" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="36">
       <c r="A32" s="5" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="24">
       <c r="A33" s="5" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="24">
       <c r="A34" s="5" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="24">
       <c r="A35" s="5" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="36">
       <c r="A36" s="5" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="24">
       <c r="A37" s="5" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="36">
       <c r="A38" s="5" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="24">
       <c r="A39" s="5" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="36">
       <c r="A40" s="5" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="36">
       <c r="A41" s="5" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="36">
       <c r="A42" s="5" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="24">
       <c r="A43" s="5" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="24">
       <c r="A44" s="5" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B44" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="G44" s="13" t="s">
         <v>193</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="24">
       <c r="A45" s="5" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F45" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="G45" s="13" t="s">
         <v>197</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="24">
       <c r="A46" s="5" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="36">
       <c r="A47" s="5" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="36">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="24">
       <c r="A48" s="5" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="24">
       <c r="A49" s="5" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="24">
       <c r="A50" s="5" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="24">
       <c r="A51" s="5" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="24">
       <c r="A52" s="5" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
